--- a/extraction-tracker.xlsx
+++ b/extraction-tracker.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Extraction Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extraction Tracker'!$A$1:$H$121</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,15 +35,10 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,11 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a1f3a"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00e8e8e8"/>
       </patternFill>
     </fill>
     <fill>
@@ -95,19 +87,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -475,10 +465,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
@@ -533,16 +523,26 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Module 0: Introduction</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+          <t>Module 0</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Fraction Gymnastics</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -554,9 +554,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Continued Fraction</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n">
         <v>8</v>
       </c>
@@ -565,24 +569,28 @@
       <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Comparing Fractions</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -594,9 +602,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>8</v>
       </c>
@@ -605,24 +617,24 @@
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -631,10 +643,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="5" t="n">
@@ -645,24 +657,24 @@
       <c r="H7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="B8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -674,7 +686,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="5" t="n">
@@ -685,24 +697,24 @@
       <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="B10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -714,7 +726,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="5" t="n">
@@ -725,24 +737,24 @@
       <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -754,7 +766,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="5" t="n">
@@ -765,24 +777,24 @@
       <c r="H13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -794,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="5" t="n">
@@ -805,24 +817,24 @@
       <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr"/>
+      <c r="B16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -831,10 +843,10 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="5" t="n">
@@ -845,24 +857,24 @@
       <c r="H17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="B18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -874,7 +886,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="5" t="n">
@@ -885,24 +897,24 @@
       <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Module 0</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
+      <c r="B20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -914,7 +926,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="5" t="n">
@@ -925,38 +937,76 @@
       <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Module 0</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Module 1</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Fraction Gymnastics</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Module 1</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Continued Fraction</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Module 1: Algebra Basics</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
+          <t>Module 1</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Comparing Fractions</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -968,11 +1018,11 @@
         <v>1</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Fraction Gymnastics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -983,28 +1033,24 @@
       <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Continued Fraction</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1013,16 +1059,12 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Comparing Fractions</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="5" t="n">
         <v>8</v>
       </c>
@@ -1031,28 +1073,24 @@
       <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="6" t="inlineStr"/>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr"/>
+      <c r="B28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1061,10 +1099,10 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="5" t="n">
@@ -1075,24 +1113,24 @@
       <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr"/>
+      <c r="B30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1104,7 +1142,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="5" t="n">
@@ -1115,24 +1153,24 @@
       <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
+      <c r="B32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1141,10 +1179,10 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="5" t="n">
@@ -1155,24 +1193,24 @@
       <c r="H33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F34" s="6" t="inlineStr"/>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr"/>
+      <c r="B34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1184,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="5" t="n">
@@ -1195,24 +1233,24 @@
       <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F36" s="6" t="inlineStr"/>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr"/>
+      <c r="B36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1221,10 +1259,10 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="5" t="n">
@@ -1235,24 +1273,24 @@
       <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F38" s="6" t="inlineStr"/>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr"/>
+      <c r="B38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1261,10 +1299,10 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="5" t="n">
@@ -1275,24 +1313,24 @@
       <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Module 1</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr"/>
+      <c r="B40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1304,7 +1342,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="5" t="n">
@@ -1315,36 +1353,36 @@
       <c r="H41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Module 1</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Module 2</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="5" t="n">
@@ -1355,38 +1393,64 @@
       <c r="H43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Module 1</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F44" s="6" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr"/>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Module 2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Module 2</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Module 2: Geometry Tools</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+          <t>Module 2</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -1395,7 +1459,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>1</v>
@@ -1409,24 +1473,24 @@
       <c r="H47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Module 2</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F48" s="6" t="inlineStr"/>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr"/>
+      <c r="B48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -1435,7 +1499,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" s="5" t="n">
         <v>3</v>
@@ -1449,24 +1513,24 @@
       <c r="H49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Module 2</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" s="6" t="inlineStr"/>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="6" t="inlineStr"/>
+      <c r="B50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -1475,7 +1539,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" s="5" t="n">
         <v>5</v>
@@ -1489,24 +1553,24 @@
       <c r="H51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Module 2</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr"/>
-      <c r="E52" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F52" s="6" t="inlineStr"/>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr"/>
+      <c r="B52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -1515,7 +1579,7 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" s="5" t="n">
         <v>2</v>
@@ -1529,24 +1593,24 @@
       <c r="H53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Module 2</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr"/>
-      <c r="E54" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F54" s="6" t="inlineStr"/>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr"/>
+      <c r="B54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -1555,7 +1619,7 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" s="5" t="n">
         <v>4</v>
@@ -1569,24 +1633,24 @@
       <c r="H55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Module 2</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7" t="n">
+      <c r="B56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D56" s="6" t="inlineStr"/>
-      <c r="E56" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F56" s="6" t="inlineStr"/>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="6" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -1595,7 +1659,7 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" s="5" t="n">
         <v>1</v>
@@ -1609,24 +1673,24 @@
       <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Module 2</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr"/>
-      <c r="E58" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F58" s="6" t="inlineStr"/>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr"/>
+      <c r="B58" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -1635,7 +1699,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" s="5" t="n">
         <v>3</v>
@@ -1649,24 +1713,24 @@
       <c r="H59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Module 2</t>
         </is>
       </c>
-      <c r="B60" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr"/>
-      <c r="E60" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F60" s="6" t="inlineStr"/>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr"/>
+      <c r="B60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -1675,7 +1739,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>5</v>
@@ -1689,33 +1753,33 @@
       <c r="H61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Module 2</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="6" t="inlineStr"/>
-      <c r="E62" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F62" s="6" t="inlineStr"/>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Module 3</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>2</v>
@@ -1729,33 +1793,33 @@
       <c r="H63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Module 2</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D64" s="6" t="inlineStr"/>
-      <c r="E64" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F64" s="6" t="inlineStr"/>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Module 3</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C65" s="5" t="n">
         <v>4</v>
@@ -1769,38 +1833,64 @@
       <c r="H65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Module 2</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C66" s="7" t="n">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Module 3</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="6" t="inlineStr"/>
-      <c r="E66" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F66" s="6" t="inlineStr"/>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Module 3</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Module 3: Algebra Tools</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
+          <t>Module 3</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -1809,10 +1899,10 @@
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="5" t="n">
@@ -1823,24 +1913,24 @@
       <c r="H69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Module 3</t>
         </is>
       </c>
-      <c r="B70" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D70" s="6" t="inlineStr"/>
-      <c r="E70" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F70" s="6" t="inlineStr"/>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr"/>
+      <c r="B70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -1849,10 +1939,10 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="5" t="n">
@@ -1863,24 +1953,24 @@
       <c r="H71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Module 3</t>
         </is>
       </c>
-      <c r="B72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr"/>
-      <c r="E72" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" s="6" t="inlineStr"/>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr"/>
+      <c r="B72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -1889,10 +1979,10 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
       <c r="E73" s="5" t="n">
@@ -1903,24 +1993,24 @@
       <c r="H73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Module 3</t>
         </is>
       </c>
-      <c r="B74" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="6" t="inlineStr"/>
-      <c r="E74" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F74" s="6" t="inlineStr"/>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr"/>
+      <c r="B74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -1929,10 +2019,10 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
       <c r="E75" s="5" t="n">
@@ -1943,24 +2033,24 @@
       <c r="H75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Module 3</t>
         </is>
       </c>
-      <c r="B76" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C76" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D76" s="6" t="inlineStr"/>
-      <c r="E76" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F76" s="6" t="inlineStr"/>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr"/>
+      <c r="B76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -1969,10 +2059,10 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="5" t="n">
@@ -1983,24 +2073,24 @@
       <c r="H77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Module 3</t>
         </is>
       </c>
-      <c r="B78" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C78" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D78" s="6" t="inlineStr"/>
-      <c r="E78" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F78" s="6" t="inlineStr"/>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr"/>
+      <c r="B78" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -2009,10 +2099,10 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="5" t="n">
@@ -2023,24 +2113,24 @@
       <c r="H79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Module 3</t>
         </is>
       </c>
-      <c r="B80" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C80" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D80" s="6" t="inlineStr"/>
-      <c r="E80" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F80" s="6" t="inlineStr"/>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr"/>
+      <c r="B80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -2049,10 +2139,10 @@
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
       <c r="E81" s="5" t="n">
@@ -2063,36 +2153,36 @@
       <c r="H81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Module 3</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C82" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D82" s="6" t="inlineStr"/>
-      <c r="E82" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F82" s="6" t="inlineStr"/>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1A</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D83" s="4" t="inlineStr"/>
       <c r="E83" s="5" t="n">
@@ -2103,36 +2193,36 @@
       <c r="H83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>Module 3</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C84" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" s="6" t="inlineStr"/>
-      <c r="E84" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F84" s="6" t="inlineStr"/>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1A</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D85" s="4" t="inlineStr"/>
       <c r="E85" s="5" t="n">
@@ -2143,36 +2233,36 @@
       <c r="H85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Module 3</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C86" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D86" s="6" t="inlineStr"/>
-      <c r="E86" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F86" s="6" t="inlineStr"/>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1A</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="5" t="n">
@@ -2183,38 +2273,64 @@
       <c r="H87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Module 3</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C88" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
-      <c r="E88" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F88" s="6" t="inlineStr"/>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1A</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Workout 1A</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" s="4" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A: Algebra Basics</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
+          <t>Workout 1A</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -2223,10 +2339,10 @@
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="5" t="n">
@@ -2237,24 +2353,24 @@
       <c r="H91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Workout 1A</t>
         </is>
       </c>
-      <c r="B92" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" s="6" t="inlineStr"/>
-      <c r="E92" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F92" s="6" t="inlineStr"/>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr"/>
+      <c r="B92" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -2263,10 +2379,10 @@
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="5" t="n">
@@ -2277,24 +2393,24 @@
       <c r="H93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Workout 1A</t>
         </is>
       </c>
-      <c r="B94" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D94" s="6" t="inlineStr"/>
-      <c r="E94" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F94" s="6" t="inlineStr"/>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr"/>
+      <c r="B94" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -2303,10 +2419,10 @@
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
       <c r="E95" s="5" t="n">
@@ -2317,24 +2433,24 @@
       <c r="H95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Workout 1A</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C96" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" s="6" t="inlineStr"/>
-      <c r="E96" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F96" s="6" t="inlineStr"/>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr"/>
+      <c r="B96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -2343,10 +2459,10 @@
         </is>
       </c>
       <c r="B97" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="5" t="n">
@@ -2357,24 +2473,24 @@
       <c r="H97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Workout 1A</t>
         </is>
       </c>
-      <c r="B98" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C98" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D98" s="6" t="inlineStr"/>
-      <c r="E98" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F98" s="6" t="inlineStr"/>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="6" t="inlineStr"/>
+      <c r="B98" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -2383,10 +2499,10 @@
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
       <c r="E99" s="5" t="n">
@@ -2397,24 +2513,24 @@
       <c r="H99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Workout 1A</t>
         </is>
       </c>
-      <c r="B100" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C100" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D100" s="6" t="inlineStr"/>
-      <c r="E100" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F100" s="6" t="inlineStr"/>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr"/>
+      <c r="B100" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -2423,10 +2539,10 @@
         </is>
       </c>
       <c r="B101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
       <c r="E101" s="5" t="n">
@@ -2437,36 +2553,36 @@
       <c r="H101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1A</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D102" s="6" t="inlineStr"/>
-      <c r="E102" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F102" s="6" t="inlineStr"/>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1B</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="5" t="n">
@@ -2477,36 +2593,36 @@
       <c r="H103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1A</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C104" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D104" s="6" t="inlineStr"/>
-      <c r="E104" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F104" s="6" t="inlineStr"/>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1B</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="5" t="n">
@@ -2517,36 +2633,36 @@
       <c r="H105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1A</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C106" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" s="6" t="inlineStr"/>
-      <c r="E106" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F106" s="6" t="inlineStr"/>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1B</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="5" t="n">
@@ -2557,36 +2673,36 @@
       <c r="H107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1A</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C108" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D108" s="6" t="inlineStr"/>
-      <c r="E108" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F108" s="6" t="inlineStr"/>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1B</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="5" t="n">
@@ -2597,38 +2713,64 @@
       <c r="H109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1A</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C110" s="7" t="n">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Workout 1B</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Workout 1B</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D110" s="6" t="inlineStr"/>
-      <c r="E110" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F110" s="6" t="inlineStr"/>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="6" t="inlineStr"/>
+      <c r="D111" s="4" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Workout 1B: Algebra Basics</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="3" t="n"/>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
+          <t>Workout 1B</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -2637,10 +2779,10 @@
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="5" t="n">
@@ -2651,24 +2793,24 @@
       <c r="H113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Workout 1B</t>
         </is>
       </c>
-      <c r="B114" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D114" s="6" t="inlineStr"/>
-      <c r="E114" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F114" s="6" t="inlineStr"/>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr"/>
+      <c r="B114" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -2677,10 +2819,10 @@
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="5" t="n">
@@ -2691,24 +2833,24 @@
       <c r="H115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Workout 1B</t>
         </is>
       </c>
-      <c r="B116" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D116" s="6" t="inlineStr"/>
-      <c r="E116" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F116" s="6" t="inlineStr"/>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr"/>
+      <c r="B116" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -2717,10 +2859,10 @@
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="5" t="n">
@@ -2731,24 +2873,24 @@
       <c r="H117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Workout 1B</t>
         </is>
       </c>
-      <c r="B118" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C118" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" s="6" t="inlineStr"/>
-      <c r="E118" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F118" s="6" t="inlineStr"/>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr"/>
+      <c r="B118" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -2757,10 +2899,10 @@
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="5" t="n">
@@ -2771,24 +2913,24 @@
       <c r="H119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Workout 1B</t>
         </is>
       </c>
-      <c r="B120" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C120" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D120" s="6" t="inlineStr"/>
-      <c r="E120" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F120" s="6" t="inlineStr"/>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr"/>
+      <c r="B120" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -2797,10 +2939,10 @@
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="5" t="n">
@@ -2810,227 +2952,8 @@
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr"/>
     </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C122" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D122" s="6" t="inlineStr"/>
-      <c r="E122" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F122" s="6" t="inlineStr"/>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="6" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C123" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D123" s="4" t="inlineStr"/>
-      <c r="E123" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F123" s="4" t="inlineStr"/>
-      <c r="G123" s="4" t="inlineStr"/>
-      <c r="H123" s="4" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C124" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D124" s="6" t="inlineStr"/>
-      <c r="E124" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F124" s="6" t="inlineStr"/>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C125" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D125" s="4" t="inlineStr"/>
-      <c r="E125" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr"/>
-      <c r="H125" s="4" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C126" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D126" s="6" t="inlineStr"/>
-      <c r="E126" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F126" s="6" t="inlineStr"/>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C127" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D127" s="4" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="4" t="inlineStr"/>
-      <c r="H127" s="4" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C128" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" s="6" t="inlineStr"/>
-      <c r="E128" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F128" s="6" t="inlineStr"/>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C129" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D129" s="4" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="4" t="inlineStr"/>
-      <c r="H129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C130" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D130" s="6" t="inlineStr"/>
-      <c r="E130" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F130" s="6" t="inlineStr"/>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C131" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D131" s="4" t="inlineStr"/>
-      <c r="E131" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F131" s="4" t="inlineStr"/>
-      <c r="G131" s="4" t="inlineStr"/>
-      <c r="H131" s="4" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C132" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D132" s="6" t="inlineStr"/>
-      <c r="E132" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F132" s="6" t="inlineStr"/>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:H121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/extraction-tracker.xlsx
+++ b/extraction-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Extraction Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extraction Tracker'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extraction Tracker'!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -595,7 +595,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -619,7 +619,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -639,7 +639,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -659,7 +659,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -679,7 +679,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -699,7 +699,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -719,7 +719,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -739,7 +739,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -779,7 +779,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -799,7 +799,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -819,7 +819,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -839,7 +839,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -859,7 +859,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -879,7 +879,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -899,7 +899,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -919,7 +919,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Module 0</t>
+          <t>Module 1</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
@@ -939,7 +939,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -948,11 +948,7 @@
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Fraction Gymnastics</t>
-        </is>
-      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="3" t="n">
         <v>8</v>
       </c>
@@ -963,7 +959,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -972,11 +968,7 @@
       <c r="C23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Continued Fraction</t>
-        </is>
-      </c>
+      <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="5" t="n">
         <v>8</v>
       </c>
@@ -987,7 +979,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -996,11 +988,7 @@
       <c r="C24" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Comparing Fractions</t>
-        </is>
-      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="n">
         <v>8</v>
       </c>
@@ -1011,7 +999,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -1020,11 +1008,7 @@
       <c r="C25" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="5" t="n">
         <v>8</v>
       </c>
@@ -1035,7 +1019,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1055,7 +1039,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -1075,7 +1059,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -1095,7 +1079,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -1115,7 +1099,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1135,7 +1119,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -1155,7 +1139,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -1175,7 +1159,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -1195,7 +1179,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
@@ -1215,7 +1199,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -1235,7 +1219,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
@@ -1255,7 +1239,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -1275,7 +1259,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
@@ -1295,7 +1279,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
@@ -1315,7 +1299,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
@@ -1335,7 +1319,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Module 1</t>
+          <t>Module 2</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -1355,7 +1339,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
@@ -1375,7 +1359,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -1395,7 +1379,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -1415,7 +1399,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -1435,7 +1419,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -1455,7 +1439,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -1475,7 +1459,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
@@ -1495,7 +1479,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -1515,7 +1499,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
@@ -1535,7 +1519,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -1555,7 +1539,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
@@ -1575,7 +1559,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
@@ -1595,7 +1579,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
@@ -1615,7 +1599,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -1635,7 +1619,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
@@ -1655,7 +1639,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
@@ -1675,7 +1659,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
@@ -1695,7 +1679,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
@@ -1715,7 +1699,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
@@ -1735,7 +1719,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Module 2</t>
+          <t>Module 3</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -1755,7 +1739,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
@@ -1775,7 +1759,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
@@ -1795,7 +1779,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
@@ -1815,7 +1799,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -1835,7 +1819,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
@@ -1855,7 +1839,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -1875,7 +1859,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
@@ -1895,7 +1879,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -1915,7 +1899,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
@@ -1935,7 +1919,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -1955,7 +1939,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
@@ -1975,7 +1959,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -1995,7 +1979,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
@@ -2015,7 +1999,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -2035,7 +2019,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
@@ -2055,7 +2039,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -2075,7 +2059,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
@@ -2095,7 +2079,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -2115,7 +2099,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
@@ -2135,7 +2119,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Module 3</t>
+          <t>Workout 1A</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -2155,7 +2139,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
@@ -2175,7 +2159,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -2195,7 +2179,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
@@ -2215,7 +2199,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -2235,7 +2219,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
@@ -2255,7 +2239,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -2275,7 +2259,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
@@ -2295,7 +2279,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -2315,7 +2299,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
@@ -2335,7 +2319,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -2355,7 +2339,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
@@ -2375,7 +2359,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -2395,7 +2379,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
@@ -2415,7 +2399,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -2435,7 +2419,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
@@ -2455,7 +2439,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -2475,7 +2459,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
@@ -2495,7 +2479,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -2515,7 +2499,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
@@ -2535,7 +2519,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Workout 1A</t>
+          <t>Workout 1B</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -2552,408 +2536,8 @@
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr"/>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
-      <c r="E102" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C103" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D103" s="4" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr"/>
-      <c r="H103" s="4" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr"/>
-      <c r="H105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C107" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr"/>
-      <c r="H107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C109" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
-      <c r="E109" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr"/>
-      <c r="H109" s="4" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C111" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D111" s="4" t="inlineStr"/>
-      <c r="E111" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr"/>
-      <c r="H111" s="4" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C113" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D113" s="4" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr"/>
-      <c r="H113" s="4" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C115" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D115" s="4" t="inlineStr"/>
-      <c r="E115" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr"/>
-      <c r="H115" s="4" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
-      <c r="E116" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C117" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D117" s="4" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr"/>
-      <c r="H117" s="4" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C119" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D119" s="4" t="inlineStr"/>
-      <c r="E119" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F119" s="4" t="inlineStr"/>
-      <c r="G119" s="4" t="inlineStr"/>
-      <c r="H119" s="4" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
-      <c r="E120" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Workout 1B</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C121" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D121" s="4" t="inlineStr"/>
-      <c r="E121" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="4" t="inlineStr"/>
-      <c r="H121" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H121"/>
+  <autoFilter ref="A1:H101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>